--- a/models/QIPEDC.xlsx
+++ b/models/QIPEDC.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Địa chỉ</t>
+          <t>D0001B</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tỉnh</t>
+          <t>D0002</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tiếp tân</t>
+          <t>D0003</t>
         </is>
       </c>
     </row>
